--- a/planilhas/Modelo_Importacao_Escalas.xlsx
+++ b/planilhas/Modelo_Importacao_Escalas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leonardo.silva\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leonardo.silva\Documents\APP FERIAS PRICING\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C4A9E1-1DB2-4C30-952D-4F80BFB706E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615B36C7-C477-43C5-ACE5-58ED405498D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Escala_Modelo" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="16">
   <si>
     <t>Colaborador</t>
   </si>
@@ -50,6 +50,24 @@
   </si>
   <si>
     <t>(61) 998691732</t>
+  </si>
+  <si>
+    <t>Edimilton Gualberto</t>
+  </si>
+  <si>
+    <t>(61) 983551360</t>
+  </si>
+  <si>
+    <t>Carolina Lima</t>
+  </si>
+  <si>
+    <t>(61) 983454986</t>
+  </si>
+  <si>
+    <t>Renan Silva</t>
+  </si>
+  <si>
+    <t>(61) 993403813</t>
   </si>
 </sst>
 </file>
@@ -427,14 +445,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -448,7 +466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -462,7 +480,7 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -476,7 +494,7 @@
         <v>46271</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -490,7 +508,7 @@
         <v>46313</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -504,7 +522,7 @@
         <v>46362</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -518,7 +536,7 @@
         <v>46264</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -532,7 +550,7 @@
         <v>46306</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -546,7 +564,7 @@
         <v>46348</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -560,7 +578,7 @@
         <v>46373</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -574,7 +592,7 @@
         <v>46250</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -588,7 +606,7 @@
         <v>46285</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -602,7 +620,7 @@
         <v>46327</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -614,6 +632,146 @@
       </c>
       <c r="D13" s="1">
         <v>46369</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46242</v>
+      </c>
+      <c r="D14" s="1">
+        <v>46243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46277</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46289</v>
+      </c>
+      <c r="D16" s="1">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46293</v>
+      </c>
+      <c r="D17" s="1">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46256</v>
+      </c>
+      <c r="D18" s="1">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46298</v>
+      </c>
+      <c r="D19" s="1">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46340</v>
+      </c>
+      <c r="D20" s="1">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46291</v>
+      </c>
+      <c r="D21" s="1">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46333</v>
+      </c>
+      <c r="D22" s="1">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46375</v>
+      </c>
+      <c r="D23" s="1">
+        <v>46376</v>
       </c>
     </row>
   </sheetData>
